--- a/Zinc/6. Statistical data analysis/Multiple linear regression/MLR.xlsx
+++ b/Zinc/6. Statistical data analysis/Multiple linear regression/MLR.xlsx
@@ -6,13 +6,15 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Final_Table" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Full_Model_Coefficients" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Full_Model_Summary" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t xml:space="preserve">Predictor</t>
   </si>
@@ -60,6 +62,42 @@
   </si>
   <si>
     <t xml:space="preserve">log_SO4_nM_std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Std. Error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pr(&gt;|t|)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Intercept)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Residual standard error</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R-squared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adjusted R-squared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F-statistic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numerator df</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Denominator df</t>
   </si>
 </sst>
 </file>
@@ -596,4 +634,303 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-0.0000000000000000617781055114893</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.0125495419681964</v>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.00000000000000492273787107531</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.999999999999996</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.926129393360342</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0155685705205599</v>
+      </c>
+      <c r="D3" t="n">
+        <v>59.4871181099956</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000407445292713326</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-0.045902911120325</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0137915474323035</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-3.32833652972168</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.000968206680282881</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="n">
+        <v>0.171555958972215</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.0151480361796393</v>
+      </c>
+      <c r="D5" t="n">
+        <v>11.3252937171358</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.000000000000000000000000174427624549752</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-0.433480863024706</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0195327863536029</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-22.1924744978715</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000002348995250765</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-0.0306781682211757</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0366870030113996</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.836213528034526</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.403615260024787</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-0.105116944474928</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.040792112005142</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-2.5768938970769</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.0103853856747688</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-0.388232447015612</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.0379593457391267</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-10.2275853141336</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.00000000000000000000129760820114478</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.00434951235588958</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.0270789781729081</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.160623208457739</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.872484456559793</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="n">
+        <v>0.0286183582210191</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0253418361627276</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.12929300139311</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.259561121620467</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0788965001548262</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.0551794495247269</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.42981673130812</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.153677191547443</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-0.0542583840178608</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0284125917325186</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.9096597919915</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.0570085786456517</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0.236784284287834</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="n">
+        <v>0.945670483756954</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0.943933202714298</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="n">
+        <v>544.339378913288</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" t="n">
+        <v>344</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/Zinc/6. Statistical data analysis/Multiple linear regression/MLR.xlsx
+++ b/Zinc/6. Statistical data analysis/Multiple linear regression/MLR.xlsx
@@ -1,111 +1,118 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ornl-my.sharepoint.com/personal/q4q_ornl_gov/Documents/Research/Bioavailability Project/BLM_spatial_assessmt/Zinc/6. Statistical data analysis/Multiple linear regression/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_044ED4BECF84B54209C862948DCB416B611A8740" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7F95604-E1DD-4320-B2D4-53721A32A7FD}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Final_Table" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Full_Model_Coefficients" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Full_Model_Summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Final_Table" sheetId="1" r:id="rId1"/>
+    <sheet name="Full_Model_Coefficients" sheetId="2" r:id="rId2"/>
+    <sheet name="Full_Model_Summary" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
-  <si>
-    <t xml:space="preserve">Predictor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p_value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VIF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rel_Importance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Zn_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_DOC_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Ca_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_DIC_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Cl_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Na_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Mg_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_K_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pH_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_Temp_C_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_SO4_nM_std</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Std. Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pr(&gt;|t|)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(Intercept)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Metric</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Residual standard error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R-squared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adjusted R-squared</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F-statistic</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Numerator df</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Denominator df</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="28">
+  <si>
+    <t>Predictor</t>
+  </si>
+  <si>
+    <t>Estimate</t>
+  </si>
+  <si>
+    <t>p_value</t>
+  </si>
+  <si>
+    <t>VIF</t>
+  </si>
+  <si>
+    <t>Rel_Importance</t>
+  </si>
+  <si>
+    <t>log_Zn_nM_std</t>
+  </si>
+  <si>
+    <t>log_DOC_nM_std</t>
+  </si>
+  <si>
+    <t>log_Ca_nM_std</t>
+  </si>
+  <si>
+    <t>log_DIC_nM_std</t>
+  </si>
+  <si>
+    <t>log_Cl_nM_std</t>
+  </si>
+  <si>
+    <t>log_Na_nM_std</t>
+  </si>
+  <si>
+    <t>log_Mg_nM_std</t>
+  </si>
+  <si>
+    <t>log_K_nM_std</t>
+  </si>
+  <si>
+    <t>pH_std</t>
+  </si>
+  <si>
+    <t>log_Temp_C_std</t>
+  </si>
+  <si>
+    <t>log_SO4_nM_std</t>
+  </si>
+  <si>
+    <t>Std. Error</t>
+  </si>
+  <si>
+    <t>t value</t>
+  </si>
+  <si>
+    <t>Pr(&gt;|t|)</t>
+  </si>
+  <si>
+    <t>(Intercept)</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Residual standard error</t>
+  </si>
+  <si>
+    <t>R-squared</t>
+  </si>
+  <si>
+    <t>Adjusted R-squared</t>
+  </si>
+  <si>
+    <t>F-statistic</t>
+  </si>
+  <si>
+    <t>Numerator df</t>
+  </si>
+  <si>
+    <t>Denominator df</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -141,6 +148,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -422,11 +438,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -443,205 +459,205 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.926129393360342</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000407445292713326</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1.53468794232318</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.627811922222818</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="B2">
+        <v>0.92612939336034195</v>
+      </c>
+      <c r="C2">
+        <v>4.0744529271332596E-183</v>
+      </c>
+      <c r="D2">
+        <v>1.5346879423231801</v>
+      </c>
+      <c r="E2">
+        <v>0.62781192222281801</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="n">
-        <v>-0.433480863024706</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000002348995250765</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.41574452667446</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="B3">
+        <v>-0.43348086302470601</v>
+      </c>
+      <c r="C3">
+        <v>2.3489952507650002E-68</v>
+      </c>
+      <c r="D3">
+        <v>2.4157445266744602</v>
+      </c>
+      <c r="E3">
         <v>0.106159633885843</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="n">
-        <v>-0.388232447015612</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.00000000000000000000129760820114478</v>
-      </c>
-      <c r="D4" t="n">
-        <v>9.12346985271894</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0963804952953663</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4">
+        <v>-0.38823244701561199</v>
+      </c>
+      <c r="C4">
+        <v>1.2976082011447801E-21</v>
+      </c>
+      <c r="D4">
+        <v>9.1234698527189408</v>
+      </c>
+      <c r="E4">
+        <v>9.6380495295366297E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="n">
-        <v>-0.0306781682211757</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.403615260024787</v>
-      </c>
-      <c r="D5" t="n">
-        <v>8.52210881603353</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.0472849528339963</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5">
+        <v>-3.0678168221175701E-2</v>
+      </c>
+      <c r="C5">
+        <v>0.40361526002478698</v>
+      </c>
+      <c r="D5">
+        <v>8.5221088160335299</v>
+      </c>
+      <c r="E5">
+        <v>4.7284952833996301E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>-0.105116944474928</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.0103853856747688</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>1.03853856747688E-2</v>
+      </c>
+      <c r="D6">
         <v>10.5359812090401</v>
       </c>
-      <c r="E6" t="n">
-        <v>0.0235157874452878</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="E6">
+        <v>2.3515787445287799E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>10</v>
       </c>
-      <c r="B7" t="n">
-        <v>0.0788965001548262</v>
-      </c>
-      <c r="C7" t="n">
+      <c r="B7">
+        <v>7.8896500154826202E-2</v>
+      </c>
+      <c r="C7">
         <v>0.153677191547443</v>
       </c>
-      <c r="D7" t="n">
-        <v>19.2786816444938</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.022195984175227</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="D7">
+        <v>19.278681644493801</v>
+      </c>
+      <c r="E7">
+        <v>2.2195984175227002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" t="n">
-        <v>-0.00434951235588958</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.872484456559793</v>
-      </c>
-      <c r="D8" t="n">
-        <v>4.64287668473474</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.0198299508562585</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="B8">
+        <v>-4.3495123558895798E-3</v>
+      </c>
+      <c r="C8">
+        <v>0.87248445655979301</v>
+      </c>
+      <c r="D8">
+        <v>4.6428766847347402</v>
+      </c>
+      <c r="E8">
+        <v>1.9829950856258501E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="n">
-        <v>-0.0542583840178608</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0570085786456517</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.11145222938304</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.0190055329916806</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="B9">
+        <v>-5.4258384017860803E-2</v>
+      </c>
+      <c r="C9">
+        <v>5.7008578645651703E-2</v>
+      </c>
+      <c r="D9">
+        <v>5.1114522293830396</v>
+      </c>
+      <c r="E9">
+        <v>1.9005532991680601E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B10" t="n">
-        <v>0.171555958972215</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.000000000000000000000000174427624549752</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.4528984885704</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.0161066567000011</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="B10">
+        <v>0.17155595897221501</v>
+      </c>
+      <c r="C10">
+        <v>1.7442762454975201E-25</v>
+      </c>
+      <c r="D10">
+        <v>1.4528984885703999</v>
+      </c>
+      <c r="E10">
+        <v>1.6106656700001099E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="n">
-        <v>-0.045902911120325</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.000968206680282881</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.20433858136969</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.0132772623722509</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="B11">
+        <v>-4.5902911120324998E-2</v>
+      </c>
+      <c r="C11">
+        <v>9.6820668028288102E-4</v>
+      </c>
+      <c r="D11">
+        <v>1.2043385813696901</v>
+      </c>
+      <c r="E11">
+        <v>1.32772623722509E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12" t="n">
-        <v>0.0286183582210191</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.259561121620467</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="B12">
+        <v>2.8618358221019099E-2</v>
+      </c>
+      <c r="C12">
+        <v>0.25956112162046702</v>
+      </c>
+      <c r="D12">
         <v>4.06629387395233</v>
       </c>
-      <c r="E12" t="n">
-        <v>0.00843182122127061</v>
+      <c r="E12">
+        <v>8.4318212212706103E-3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E13"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -658,222 +674,225 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
-      <c r="B2" t="n">
-        <v>-0.0000000000000000617781055114893</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.0125495419681964</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-0.00000000000000492273787107531</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="B2">
+        <v>-6.1778105511489299E-17</v>
+      </c>
+      <c r="C2">
+        <v>1.2549541968196401E-2</v>
+      </c>
+      <c r="D2">
+        <v>-4.9227378710753101E-15</v>
+      </c>
+      <c r="E2">
         <v>0.999999999999996</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.926129393360342</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.0155685705205599</v>
-      </c>
-      <c r="D3" t="n">
-        <v>59.4871181099956</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000407445292713326</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="B3">
+        <v>0.92612939336034195</v>
+      </c>
+      <c r="C3">
+        <v>1.5568570520559899E-2</v>
+      </c>
+      <c r="D3">
+        <v>59.487118109995599</v>
+      </c>
+      <c r="E3">
+        <v>4.0744529271332596E-183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="n">
-        <v>-0.045902911120325</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.0137915474323035</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="B4">
+        <v>-4.5902911120324998E-2</v>
+      </c>
+      <c r="C4">
+        <v>1.37915474323035E-2</v>
+      </c>
+      <c r="D4">
         <v>-3.32833652972168</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.000968206680282881</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="E4">
+        <v>9.6820668028288102E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="B5" t="n">
-        <v>0.171555958972215</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.0151480361796393</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="B5">
+        <v>0.17155595897221501</v>
+      </c>
+      <c r="C5">
+        <v>1.51480361796393E-2</v>
+      </c>
+      <c r="D5">
         <v>11.3252937171358</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.000000000000000000000000174427624549752</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="E5">
+        <v>1.7442762454975201E-25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" t="n">
-        <v>-0.433480863024706</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.0195327863536029</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-22.1924744978715</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000002348995250765</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="B6">
+        <v>-0.43348086302470601</v>
+      </c>
+      <c r="C6">
+        <v>1.95327863536029E-2</v>
+      </c>
+      <c r="D6">
+        <v>-22.192474497871501</v>
+      </c>
+      <c r="E6">
+        <v>2.3489952507650002E-68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="n">
-        <v>-0.0306781682211757</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.0366870030113996</v>
-      </c>
-      <c r="D7" t="n">
-        <v>-0.836213528034526</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.403615260024787</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="B7">
+        <v>-3.0678168221175701E-2</v>
+      </c>
+      <c r="C7">
+        <v>3.6687003011399599E-2</v>
+      </c>
+      <c r="D7">
+        <v>-0.83621352803452598</v>
+      </c>
+      <c r="E7">
+        <v>0.40361526002478698</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8">
         <v>-0.105116944474928</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.040792112005142</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="C8">
+        <v>4.0792112005142003E-2</v>
+      </c>
+      <c r="D8">
         <v>-2.5768938970769</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.0103853856747688</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="E8">
+        <v>1.03853856747688E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B9" t="n">
-        <v>-0.388232447015612</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.0379593457391267</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B9">
+        <v>-0.38823244701561199</v>
+      </c>
+      <c r="C9">
+        <v>3.7959345739126703E-2</v>
+      </c>
+      <c r="D9">
         <v>-10.2275853141336</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.00000000000000000000129760820114478</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="E9">
+        <v>1.2976082011447801E-21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10" t="n">
-        <v>-0.00434951235588958</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.0270789781729081</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="B10">
+        <v>-4.3495123558895798E-3</v>
+      </c>
+      <c r="C10">
+        <v>2.7078978172908101E-2</v>
+      </c>
+      <c r="D10">
         <v>-0.160623208457739</v>
       </c>
-      <c r="E10" t="n">
-        <v>0.872484456559793</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="E10">
+        <v>0.87248445655979301</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="B11" t="n">
-        <v>0.0286183582210191</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.0253418361627276</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="B11">
+        <v>2.8618358221019099E-2</v>
+      </c>
+      <c r="C11">
+        <v>2.5341836162727598E-2</v>
+      </c>
+      <c r="D11">
         <v>1.12929300139311</v>
       </c>
-      <c r="E11" t="n">
-        <v>0.259561121620467</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="E11">
+        <v>0.25956112162046702</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
-      <c r="B12" t="n">
-        <v>0.0788965001548262</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.0551794495247269</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="B12">
+        <v>7.8896500154826202E-2</v>
+      </c>
+      <c r="C12">
+        <v>5.5179449524726899E-2</v>
+      </c>
+      <c r="D12">
         <v>1.42981673130812</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>0.153677191547443</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
-        <v>-0.0542583840178608</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.0284125917325186</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-1.9096597919915</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.0570085786456517</v>
+      <c r="B13">
+        <v>-5.4258384017860803E-2</v>
+      </c>
+      <c r="C13">
+        <v>2.8412591732518599E-2</v>
+      </c>
+      <c r="D13">
+        <v>-1.9096597919914999</v>
+      </c>
+      <c r="E13">
+        <v>5.7008578645651703E-2</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="11.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -881,56 +900,56 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="n">
-        <v>0.236784284287834</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="B2">
+        <v>0.23678428428783399</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="n">
-        <v>0.945670483756954</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="B3">
+        <v>0.94567048375695395</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" t="n">
-        <v>0.943933202714298</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="B4">
+        <v>0.94393320271429804</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>25</v>
       </c>
-      <c r="B5" t="n">
-        <v>544.339378913288</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="B5">
+        <v>544.33937891328799</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6">
         <v>11</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7">
         <v>344</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>